--- a/data/trans_camb/POLIPATOLOGIA_2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_2-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 9,82</t>
+          <t>-1,36; 9,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 12,7</t>
+          <t>2,28; 13,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 19,29</t>
+          <t>9,26; 19,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 6,45</t>
+          <t>-7,22; 5,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 8,96</t>
+          <t>-4,33; 8,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 23,51</t>
+          <t>10,9; 23,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 7,01</t>
+          <t>-1,77; 6,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,71</t>
+          <t>1,44; 10,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 20,26</t>
+          <t>11,8; 20,16</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 79,73</t>
+          <t>-8,05; 72,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 95,34</t>
+          <t>12,7; 98,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,47; 149,82</t>
+          <t>51,4; 158,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 34,59</t>
+          <t>-28,12; 31,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 48,41</t>
+          <t>-17,4; 47,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,31; 129,85</t>
+          <t>41,4; 124,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 42,6</t>
+          <t>-8,82; 40,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 59,74</t>
+          <t>6,15; 64,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60,24; 126,42</t>
+          <t>58,37; 126,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 10,85</t>
+          <t>0,19; 11,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 12,51</t>
+          <t>0,16; 11,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 24,67</t>
+          <t>12,46; 24,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 9,72</t>
+          <t>-3,06; 9,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 4,03</t>
+          <t>-8,48; 3,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 21,65</t>
+          <t>8,83; 21,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 7,93</t>
+          <t>-0,72; 8,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 5,83</t>
+          <t>-2,36; 6,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,47; 20,77</t>
+          <t>11,74; 20,87</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 86,88</t>
+          <t>0,8; 91,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 100,29</t>
+          <t>0,89; 92,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,88; 203,24</t>
+          <t>67,51; 198,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 44,29</t>
+          <t>-12,3; 43,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 18,21</t>
+          <t>-30,51; 18,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,69; 100,52</t>
+          <t>30,58; 102,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 45,75</t>
+          <t>-2,82; 45,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 32,42</t>
+          <t>-11,2; 34,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,72; 117,6</t>
+          <t>53,88; 117,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 12,59</t>
+          <t>2,78; 12,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 10,05</t>
+          <t>-0,76; 10,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 16,13</t>
+          <t>-14,55; 15,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 13,46</t>
+          <t>-5,2; 13,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 12,47</t>
+          <t>-7,78; 13,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,05; 32,48</t>
+          <t>13,34; 32,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 11,7</t>
+          <t>2,8; 11,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 9,09</t>
+          <t>-0,53; 8,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 18,2</t>
+          <t>-11,73; 18,14</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,19; 61,56</t>
+          <t>10,38; 63,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 49,99</t>
+          <t>-3,5; 50,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-60,0; 74,7</t>
+          <t>-59,53; 70,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 45,92</t>
+          <t>-13,46; 44,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 44,04</t>
+          <t>-20,81; 45,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,87; 119,0</t>
+          <t>33,82; 118,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,54; 52,32</t>
+          <t>9,85; 51,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 38,51</t>
+          <t>-2,41; 38,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 73,58</t>
+          <t>-44,51; 73,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 6,92</t>
+          <t>-0,43; 6,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 4,21</t>
+          <t>-3,31; 3,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 13,97</t>
+          <t>6,2; 13,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 5,27</t>
+          <t>-4,49; 5,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 4,32</t>
+          <t>-5,08; 4,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,27; 48,38</t>
+          <t>11,86; 45,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,08</t>
+          <t>-0,51; 5,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,01</t>
+          <t>-2,61; 2,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,45; 33,17</t>
+          <t>10,56; 36,64</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 29,11</t>
+          <t>-1,46; 29,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 17,89</t>
+          <t>-12,07; 16,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23,27; 57,71</t>
+          <t>22,59; 59,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 20,27</t>
+          <t>-13,99; 19,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 16,35</t>
+          <t>-16,41; 16,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,67; 180,83</t>
+          <t>39,93; 173,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 20,3</t>
+          <t>-1,89; 20,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 12,1</t>
+          <t>-9,64; 11,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,54; 130,14</t>
+          <t>38,86; 149,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 8,46</t>
+          <t>-3,0; 8,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 13,26</t>
+          <t>1,54; 13,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,62; 21,84</t>
+          <t>8,37; 21,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,21; 17,56</t>
+          <t>6,58; 17,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,88; 16,78</t>
+          <t>5,88; 16,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,52; 33,31</t>
+          <t>15,51; 33,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,33</t>
+          <t>4,18; 12,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,84; 12,61</t>
+          <t>4,82; 12,67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,02; 28,71</t>
+          <t>14,78; 29,17</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 46,84</t>
+          <t>-12,42; 51,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6,83; 74,38</t>
+          <t>5,94; 74,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34,29; 122,25</t>
+          <t>32,76; 118,3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,89; 56,57</t>
+          <t>17,59; 55,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,99; 54,47</t>
+          <t>15,21; 54,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,06; 104,26</t>
+          <t>41,48; 103,08</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,0; 45,22</t>
+          <t>13,48; 46,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15,54; 46,68</t>
+          <t>15,27; 46,53</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>48,24; 102,76</t>
+          <t>47,13; 102,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 7,33</t>
+          <t>-0,2; 7,14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 5,23</t>
+          <t>-0,71; 5,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,64; 21,75</t>
+          <t>5,48; 21,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,72; 10,89</t>
+          <t>2,85; 11,31</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 5,98</t>
+          <t>-2,13; 6,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,34; 10,04</t>
+          <t>1,57; 10,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,54</t>
+          <t>2,55; 10,03</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 4,7</t>
+          <t>-2,3; 5,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,85</t>
+          <t>1,29; 9,39</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 389,04</t>
+          <t>-13,75; 408,0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 280,19</t>
+          <t>-25,49; 328,25</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>112,78; 1095,36</t>
+          <t>110,16; 1183,09</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,54; 27,54</t>
+          <t>6,81; 28,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 14,9</t>
+          <t>-4,79; 15,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,11; 25,29</t>
+          <t>3,34; 25,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,23; 29,81</t>
+          <t>6,92; 30,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 15,03</t>
+          <t>-6,42; 15,67</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4,29; 30,21</t>
+          <t>3,65; 29,18</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,7</t>
+          <t>2,4; 6,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,23</t>
+          <t>2,23; 6,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,99; 14,04</t>
+          <t>4,82; 13,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,45</t>
+          <t>2,63; 7,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,08</t>
+          <t>0,15; 5,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,54; 27,02</t>
+          <t>12,5; 25,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,31</t>
+          <t>3,29; 6,51</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,88</t>
+          <t>1,7; 4,84</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,67; 19,53</t>
+          <t>9,53; 18,95</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,6; 36,18</t>
+          <t>11,59; 34,03</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>9,41; 32,9</t>
+          <t>10,75; 33,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20,31; 72,66</t>
+          <t>23,7; 72,89</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8,06; 23,06</t>
+          <t>7,75; 22,99</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,3; 15,79</t>
+          <t>0,37; 15,48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,02; 80,75</t>
+          <t>36,09; 77,43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,45; 24,23</t>
+          <t>11,65; 24,99</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>6,47; 18,92</t>
+          <t>6,17; 18,77</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>35,54; 74,13</t>
+          <t>34,5; 71,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_2-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,39</t>
+          <t>14,98</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,31</t>
+          <t>17,53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,27</t>
+          <t>16,69</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 9,52</t>
+          <t>-0,83; 9,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,12</t>
+          <t>2,3; 13,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 19,97</t>
+          <t>10,05; 19,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 5,93</t>
+          <t>-7,25; 6,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 8,74</t>
+          <t>-4,63; 8,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,9; 23,04</t>
+          <t>10,76; 23,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 6,44</t>
+          <t>-1,95; 6,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 10,59</t>
+          <t>1,19; 9,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,8; 20,16</t>
+          <t>12,95; 20,66</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>91,89%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 72,48</t>
+          <t>-5,17; 67,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,7; 98,92</t>
+          <t>12,22; 97,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,4; 158,19</t>
+          <t>53,47; 152,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 31,36</t>
+          <t>-28,72; 35,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 47,13</t>
+          <t>-18,2; 46,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,4; 124,22</t>
+          <t>40,04; 128,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 40,96</t>
+          <t>-9,8; 39,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 64,58</t>
+          <t>5,98; 58,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,37; 126,58</t>
+          <t>61,59; 127,71</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18,46</t>
+          <t>17,88</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,56</t>
+          <t>16,21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16,7</t>
+          <t>16,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 11,19</t>
+          <t>-0,13; 11,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 11,48</t>
+          <t>0,27; 11,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,46; 24,22</t>
+          <t>12,03; 23,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 9,48</t>
+          <t>-3,82; 9,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 3,79</t>
+          <t>-8,9; 3,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 21,52</t>
+          <t>10,75; 22,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 8,0</t>
+          <t>-0,51; 7,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 6,32</t>
+          <t>-2,47; 5,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,74; 20,87</t>
+          <t>12,49; 21,1</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123,43%</t>
+          <t>119,55%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 91,38</t>
+          <t>-0,81; 89,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 92,69</t>
+          <t>1,67; 96,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,51; 198,81</t>
+          <t>68,37; 198,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 43,03</t>
+          <t>-14,44; 41,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 18,16</t>
+          <t>-32,33; 16,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,58; 102,64</t>
+          <t>36,53; 106,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 45,35</t>
+          <t>-2,44; 44,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 34,57</t>
+          <t>-11,1; 32,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,88; 117,4</t>
+          <t>56,72; 121,26</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>12,91</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,37</t>
+          <t>22,0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>16,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 12,8</t>
+          <t>2,39; 12,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 10,0</t>
+          <t>-0,65; 9,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 15,55</t>
+          <t>7,24; 18,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 13,01</t>
+          <t>-4,46; 14,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 13,25</t>
+          <t>-7,95; 13,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,34; 32,45</t>
+          <t>11,96; 31,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 11,93</t>
+          <t>2,95; 12,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 8,87</t>
+          <t>-0,68; 9,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 18,14</t>
+          <t>11,16; 20,75</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>63,76%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,38; 63,82</t>
+          <t>9,19; 63,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 50,37</t>
+          <t>-2,47; 47,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 70,82</t>
+          <t>29,43; 92,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 44,72</t>
+          <t>-11,82; 51,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 45,73</t>
+          <t>-20,04; 46,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,82; 118,81</t>
+          <t>30,01; 111,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 51,58</t>
+          <t>10,42; 52,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 38,32</t>
+          <t>-2,7; 39,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,51; 73,64</t>
+          <t>41,3; 91,43</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,87</t>
+          <t>9,5</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,45</t>
+          <t>13,77</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17,87</t>
+          <t>11,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 6,98</t>
+          <t>-0,43; 6,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 3,91</t>
+          <t>-3,42; 3,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,94</t>
+          <t>5,75; 13,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 5,21</t>
+          <t>-3,89; 5,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 4,37</t>
+          <t>-4,74; 4,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,86; 45,43</t>
+          <t>9,34; 18,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,02</t>
+          <t>-0,57; 5,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,95</t>
+          <t>-2,55; 3,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,56; 36,64</t>
+          <t>8,78; 14,55</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 29,44</t>
+          <t>-1,7; 29,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 16,51</t>
+          <t>-12,5; 15,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,59; 59,03</t>
+          <t>20,95; 57,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 19,42</t>
+          <t>-12,68; 22,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 16,38</t>
+          <t>-15,34; 16,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,93; 173,65</t>
+          <t>30,28; 71,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 20,06</t>
+          <t>-1,9; 20,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 11,68</t>
+          <t>-9,17; 13,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,86; 149,97</t>
+          <t>31,08; 58,73</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15,49</t>
+          <t>12,26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,81</t>
+          <t>19,96</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20,44</t>
+          <t>16,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 8,79</t>
+          <t>-3,29; 8,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 13,06</t>
+          <t>2,2; 13,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,37; 21,46</t>
+          <t>6,46; 18,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,58; 17,44</t>
+          <t>6,18; 17,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,88; 16,85</t>
+          <t>6,13; 16,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,51; 33,82</t>
+          <t>15,25; 25,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,43</t>
+          <t>4,12; 12,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,82; 12,67</t>
+          <t>4,98; 12,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,78; 29,17</t>
+          <t>12,6; 20,53</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 51,38</t>
+          <t>-13,68; 46,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5,94; 74,47</t>
+          <t>8,86; 76,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32,76; 118,3</t>
+          <t>26,26; 101,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,59; 55,75</t>
+          <t>17,0; 57,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,21; 54,06</t>
+          <t>16,56; 54,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,48; 103,08</t>
+          <t>40,4; 82,62</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,48; 46,73</t>
+          <t>13,57; 46,33</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15,27; 46,53</t>
+          <t>15,64; 47,9</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>47,13; 102,36</t>
+          <t>39,4; 76,54</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12,17</t>
+          <t>12,78</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,78</t>
+          <t>5,16</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,51</t>
+          <t>5,82</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 7,14</t>
+          <t>-0,5; 7,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 5,75</t>
+          <t>-0,77; 5,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5,48; 21,04</t>
+          <t>5,8; 21,53</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,85; 11,31</t>
+          <t>2,94; 11,45</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 6,19</t>
+          <t>-2,09; 6,42</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57; 10,45</t>
+          <t>0,65; 9,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,03</t>
+          <t>2,7; 9,7</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,07</t>
+          <t>-1,94; 5,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,29; 9,39</t>
+          <t>1,5; 9,32</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>391,95%</t>
+          <t>411,56%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 408,0</t>
+          <t>-18,36; 381,31</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-25,49; 328,25</t>
+          <t>-22,98; 314,22</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>110,16; 1183,09</t>
+          <t>122,29; 1101,58</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,81; 28,85</t>
+          <t>7,15; 29,21</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 15,79</t>
+          <t>-4,78; 16,45</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,34; 25,89</t>
+          <t>1,52; 23,94</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,92; 30,56</t>
+          <t>7,55; 30,2</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 15,67</t>
+          <t>-5,54; 16,05</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3,65; 29,18</t>
+          <t>4,22; 28,46</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>12,61</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,64</t>
+          <t>12,7</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>13,89</t>
+          <t>12,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,41</t>
+          <t>2,38; 6,51</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,21</t>
+          <t>2,15; 6,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,82; 13,96</t>
+          <t>10,46; 14,63</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,37</t>
+          <t>2,93; 7,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,0</t>
+          <t>0,21; 4,97</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,5; 25,44</t>
+          <t>10,35; 14,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,51</t>
+          <t>3,37; 6,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,84</t>
+          <t>1,9; 4,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,53; 18,95</t>
+          <t>11,17; 14,33</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>11,59; 34,03</t>
+          <t>11,54; 34,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,75; 33,44</t>
+          <t>10,45; 32,05</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>23,7; 72,89</t>
+          <t>50,29; 77,62</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,75; 22,99</t>
+          <t>8,51; 23,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,37; 15,48</t>
+          <t>0,46; 15,27</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,09; 77,43</t>
+          <t>29,52; 46,04</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,65; 24,99</t>
+          <t>12,18; 24,86</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>6,17; 18,77</t>
+          <t>6,87; 19,25</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>34,5; 71,04</t>
+          <t>40,3; 55,52</t>
         </is>
       </c>
     </row>
